--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_validation_results.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_validation_results.xlsx
@@ -13152,10 +13152,10 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
@@ -13194,7 +13194,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82.97035499999765</v>
+        <v>19.98997160000727</v>
       </c>
       <c r="B2" t="n">
         <v>60</v>
@@ -13203,7 +13203,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>2.169449286288015</v>
+        <v>9.004513106986877</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_validation_results.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_validation_results.xlsx
@@ -13155,7 +13155,7 @@
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
@@ -13194,7 +13194,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>19.98997160000727</v>
+        <v>19.79497599997558</v>
       </c>
       <c r="B2" t="n">
         <v>60</v>
@@ -13203,7 +13203,7 @@
         <v>120</v>
       </c>
       <c r="D2" t="n">
-        <v>9.004513106986877</v>
+        <v>9.09321431259683</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_validation_results.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_validation_results.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'metrics_by_scenario'!$A$1:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'regime_hysteresis'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'orp_support_stress'!$A$1:$K$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'topology_tests'!$A$1:$D$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'topology_tests'!$A$1:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'complexity'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'acceptance'!$A$1:$I$8</definedName>
   </definedNames>
@@ -636,7 +636,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O24" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O38" t="n">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O39" t="n">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O47" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O49" t="n">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O52" t="n">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O53" t="n">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O54" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O55" t="n">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O57" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O58" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O60" t="n">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O61" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O62" t="n">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O63" t="n">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O64" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O65" t="n">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O66" t="n">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O67" t="n">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O69" t="n">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O71" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O73" t="n">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O74" t="n">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O75" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O76" t="n">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O77" t="n">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O79" t="n">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O80" t="n">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O81" t="n">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O82" t="n">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O83" t="n">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O84" t="n">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O85" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O86" t="n">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O87" t="n">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O88" t="n">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O89" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O90" t="n">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O91" t="n">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O92" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O93" t="n">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O94" t="n">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O95" t="n">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O96" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O97" t="n">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O98" t="n">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O99" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O100" t="n">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O101" t="n">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O102" t="n">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O103" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O104" t="n">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O105" t="n">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O106" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O107" t="n">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O108" t="n">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O109" t="n">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O110" t="n">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O111" t="n">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O112" t="n">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O113" t="n">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O114" t="n">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O115" t="n">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O116" t="n">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O117" t="n">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O118" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O119" t="n">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O120" t="n">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O121" t="n">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O122" t="n">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O123" t="n">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O124" t="n">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O125" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O126" t="n">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O128" t="n">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O129" t="n">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O130" t="n">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O131" t="n">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O132" t="n">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O133" t="n">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O134" t="n">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O135" t="n">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O136" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O137" t="n">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O138" t="n">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O139" t="n">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O140" t="n">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O141" t="n">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O142" t="n">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O143" t="n">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O144" t="n">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O145" t="n">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O146" t="n">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O147" t="n">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O148" t="n">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O149" t="n">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O150" t="n">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O151" t="n">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O152" t="n">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O153" t="n">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O154" t="n">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O155" t="n">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O156" t="n">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O157" t="n">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O158" t="n">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O159" t="n">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O160" t="n">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O161" t="n">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O162" t="n">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O163" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O164" t="n">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O165" t="n">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O166" t="n">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O167" t="n">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O168" t="n">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O169" t="n">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O170" t="n">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O171" t="n">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O172" t="n">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O173" t="n">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O174" t="n">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O175" t="n">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O176" t="n">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O177" t="n">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O178" t="n">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O179" t="n">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O180" t="n">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.1-global-regime-candidate</t>
+          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
         </is>
       </c>
       <c r="O181" t="n">
@@ -32094,10 +32094,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
@@ -32146,7 +32146,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>pending_approval_blocks_total</t>
+          <t>research_topology_evidence_complete</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -32157,46 +32157,64 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>D7_total remains null until field drawing and two-person approval</t>
+          <t>author-confirmed line, zone, order and SCADA identity; instrument counts reconciled</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>candidate_swap_recall</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
+          <t>pending_approval_blocks_total</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
       <c r="C4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>not estimable without field-confirmed topology perturbations</t>
+          <t>D7_total remains null until documentary audit, support and dual approval</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>candidate_swap_recall</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>not estimable without field-confirmed topology perturbations</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>false_topology_alert_count</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="C5" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>report-only alerts; no automatic registry mutation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D5"/>
+  <autoFilter ref="A1:D6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32252,7 +32270,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55.79501259990502</v>
+        <v>61.13266320002731</v>
       </c>
       <c r="B2" t="n">
         <v>180</v>
@@ -32261,7 +32279,7 @@
         <v>360</v>
       </c>
       <c r="D2" t="n">
-        <v>9.678283601292271</v>
+        <v>8.833247687370708</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -32572,7 +32590,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>blocked_by_unverified_topology_asset_mapping_and_limited_support</t>
+          <t>blocked_by_production_documentary_approval_and_limited_support</t>
         </is>
       </c>
     </row>

--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_validation_results.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_validation_results.xlsx
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'orp_support_stress'!$A$1:$K$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'topology_tests'!$A$1:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'complexity'!$A$1:$F$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'acceptance'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'acceptance'!$A$1:$I$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -461,7 +461,7 @@
     <col width="45" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="42" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O24" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O38" t="n">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O39" t="n">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O47" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O49" t="n">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O52" t="n">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O53" t="n">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O54" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O55" t="n">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O57" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O58" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O60" t="n">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O61" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O62" t="n">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O63" t="n">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O64" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O65" t="n">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O66" t="n">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O67" t="n">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O69" t="n">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O71" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O73" t="n">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O74" t="n">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O75" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O76" t="n">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O77" t="n">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O79" t="n">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O80" t="n">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O81" t="n">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O82" t="n">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O83" t="n">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O84" t="n">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O85" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O86" t="n">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O87" t="n">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O88" t="n">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O89" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O90" t="n">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O91" t="n">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O92" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O93" t="n">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O94" t="n">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O95" t="n">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O96" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O97" t="n">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O98" t="n">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O99" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O100" t="n">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O101" t="n">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O102" t="n">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O103" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O104" t="n">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O105" t="n">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O106" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O107" t="n">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O108" t="n">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O109" t="n">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O110" t="n">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O111" t="n">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O112" t="n">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O113" t="n">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O114" t="n">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O115" t="n">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O116" t="n">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O117" t="n">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O118" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O119" t="n">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O120" t="n">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O121" t="n">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O122" t="n">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O123" t="n">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O124" t="n">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O125" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O126" t="n">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O128" t="n">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O129" t="n">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O130" t="n">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O131" t="n">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O132" t="n">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O133" t="n">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O134" t="n">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O135" t="n">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O136" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O137" t="n">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O138" t="n">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O139" t="n">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O140" t="n">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O141" t="n">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O142" t="n">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O143" t="n">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O144" t="n">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O145" t="n">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O146" t="n">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O147" t="n">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O148" t="n">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O149" t="n">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O150" t="n">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O151" t="n">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O152" t="n">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O153" t="n">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O154" t="n">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O155" t="n">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O156" t="n">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O157" t="n">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O158" t="n">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O159" t="n">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O160" t="n">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O161" t="n">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O162" t="n">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O163" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O164" t="n">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O165" t="n">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O166" t="n">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O167" t="n">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O168" t="n">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O169" t="n">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O170" t="n">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O171" t="n">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O172" t="n">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O173" t="n">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O174" t="n">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O175" t="n">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O176" t="n">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O177" t="n">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O178" t="n">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O179" t="n">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O180" t="n">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.1.2-author-confirmed-regime-candidate</t>
+          <t>d7-local-template-v2.2-validation-graded</t>
         </is>
       </c>
       <c r="O181" t="n">
@@ -29388,7 +29388,7 @@
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="29" customWidth="1" min="8" max="8"/>
-    <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="45" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
@@ -29466,7 +29466,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -29485,12 +29485,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K2" t="b">
@@ -29513,7 +29513,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -29532,12 +29532,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K3" t="b">
@@ -29579,12 +29579,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -29607,7 +29607,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -29626,12 +29626,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -29654,7 +29654,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -29673,12 +29673,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K6" t="b">
@@ -29701,7 +29701,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -29720,12 +29720,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -29767,12 +29767,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K8" t="b">
@@ -29795,7 +29795,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -29814,12 +29814,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -29842,7 +29842,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -29861,12 +29861,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K10" t="b">
@@ -29889,7 +29889,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -29908,12 +29908,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K11" t="b">
@@ -29955,12 +29955,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K12" t="b">
@@ -29983,7 +29983,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -30002,12 +30002,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K13" t="b">
@@ -30030,7 +30030,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -30049,12 +30049,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>statistical_action_candidate</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K14" t="b">
@@ -30096,12 +30096,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K15" t="b">
@@ -30143,12 +30143,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts</t>
         </is>
       </c>
       <c r="K16" t="b">
@@ -30171,7 +30171,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -30180,7 +30180,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
@@ -30190,12 +30190,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K17" t="b">
@@ -30218,7 +30218,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -30237,12 +30237,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>statistical_action_candidate</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K18" t="b">
@@ -30284,12 +30284,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K19" t="b">
@@ -30331,12 +30331,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts</t>
         </is>
       </c>
       <c r="K20" t="b">
@@ -30359,7 +30359,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -30368,7 +30368,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
@@ -30378,12 +30378,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K21" t="b">
@@ -30406,7 +30406,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -30425,12 +30425,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>statistical_action_candidate</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K22" t="b">
@@ -30472,12 +30472,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K23" t="b">
@@ -30519,12 +30519,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts</t>
         </is>
       </c>
       <c r="K24" t="b">
@@ -30547,7 +30547,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -30556,7 +30556,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -30566,12 +30566,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K25" t="b">
@@ -30594,7 +30594,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -30613,12 +30613,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>statistical_action_candidate</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K26" t="b">
@@ -30660,12 +30660,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K27" t="b">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts</t>
         </is>
       </c>
       <c r="K28" t="b">
@@ -30735,7 +30735,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -30744,7 +30744,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
@@ -30754,12 +30754,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K29" t="b">
@@ -30782,7 +30782,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -30801,12 +30801,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K30" t="b">
@@ -30829,7 +30829,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -30848,12 +30848,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K31" t="b">
@@ -30895,12 +30895,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K32" t="b">
@@ -30923,7 +30923,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -30942,12 +30942,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K33" t="b">
@@ -30970,7 +30970,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -30989,12 +30989,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K34" t="b">
@@ -31017,7 +31017,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -31036,12 +31036,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K35" t="b">
@@ -31083,12 +31083,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K36" t="b">
@@ -31111,7 +31111,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -31130,12 +31130,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K37" t="b">
@@ -31158,7 +31158,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -31177,12 +31177,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K38" t="b">
@@ -31205,7 +31205,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -31224,12 +31224,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K39" t="b">
@@ -31271,12 +31271,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K40" t="b">
@@ -31299,7 +31299,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -31318,12 +31318,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>not_eligible</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K41" t="b">
@@ -31346,7 +31346,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -31365,12 +31365,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>statistical_action_candidate</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K42" t="b">
@@ -31412,12 +31412,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K43" t="b">
@@ -31459,12 +31459,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts</t>
         </is>
       </c>
       <c r="K44" t="b">
@@ -31487,7 +31487,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -31496,7 +31496,7 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>1</v>
@@ -31506,12 +31506,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K45" t="b">
@@ -31534,7 +31534,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -31553,12 +31553,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>statistical_action_candidate</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K46" t="b">
@@ -31600,12 +31600,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K47" t="b">
@@ -31647,12 +31647,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts</t>
         </is>
       </c>
       <c r="K48" t="b">
@@ -31675,7 +31675,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -31684,7 +31684,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -31694,12 +31694,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K49" t="b">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -31741,12 +31741,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>statistical_action_candidate</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K50" t="b">
@@ -31788,12 +31788,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K51" t="b">
@@ -31835,12 +31835,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts</t>
         </is>
       </c>
       <c r="K52" t="b">
@@ -31863,7 +31863,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -31872,7 +31872,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
@@ -31882,12 +31882,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K53" t="b">
@@ -31910,7 +31910,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -31929,12 +31929,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>statistical_action_candidate</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>none</t>
         </is>
       </c>
       <c r="K54" t="b">
@@ -31976,12 +31976,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>holdout_far</t>
         </is>
       </c>
       <c r="K55" t="b">
@@ -32023,12 +32023,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>diagnostic_only</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|distinct_months|blocked_holdouts</t>
         </is>
       </c>
       <c r="K56" t="b">
@@ -32051,7 +32051,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -32060,7 +32060,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
@@ -32070,12 +32070,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>candidate</t>
+          <t>scientific_score_ready</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>manual_approval_and_external_validation_pending</t>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
         </is>
       </c>
       <c r="K57" t="b">
@@ -32097,7 +32097,7 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
@@ -32164,7 +32164,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>pending_approval_blocks_total</t>
+          <t>deployment_governance_separated_from_scientific_score</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -32175,7 +32175,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>D7_total remains null until documentary audit, support and dual approval</t>
+          <t>documentary approval is retained for deployment but does not suppress research D7_total</t>
         </is>
       </c>
     </row>
@@ -32231,7 +32231,7 @@
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
@@ -32270,7 +32270,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>61.13266320002731</v>
+        <v>55.16474209993612</v>
       </c>
       <c r="B2" t="n">
         <v>180</v>
@@ -32279,7 +32279,7 @@
         <v>360</v>
       </c>
       <c r="D2" t="n">
-        <v>8.833247687370708</v>
+        <v>9.788860443594441</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -32304,10 +32304,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -32572,30 +32572,86 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>production_release</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>manual</t>
-        </is>
+          <t>scientific_score_release</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <f>=</f>
+        <v/>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>blocked_by_production_documentary_approval_and_limited_support</t>
+          <t>score_release_excludes_node_localization_claim</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sensor_veto_release</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <f>=</f>
+        <v/>
+      </c>
+      <c r="E9" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>node_specific_hard_veto_requires_localization</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>deployment_release</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>documentary_approval_and_external_truth_pending</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I8"/>
+  <autoFilter ref="A1:I10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_validation_results.xlsx
+++ b/Project 1 Data Quality Assessment/D7 Topological Role Consistency and Structural Representativeness/outputs/local/D7_validation_results.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'negative_controls'!$A$1:$I$361</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'metrics_by_scenario'!$A$1:$I$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'regime_hysteresis'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'orp_support_stress'!$A$1:$K$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'orp_support_stress'!$A$1:$S$57</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'topology_tests'!$A$1:$D$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'complexity'!$A$1:$F$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'acceptance'!$A$1:$I$10</definedName>
@@ -461,7 +461,7 @@
     <col width="45" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
     <col width="22" customWidth="1" min="15" max="15"/>
     <col width="21" customWidth="1" min="16" max="16"/>
     <col width="23" customWidth="1" min="17" max="17"/>
@@ -636,7 +636,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -721,7 +721,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -806,7 +806,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O14" t="n">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O15" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O16" t="n">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O17" t="n">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O22" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O23" t="n">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O24" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O32" t="n">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O38" t="n">
@@ -3781,7 +3781,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O39" t="n">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O40" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O45" t="n">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O46" t="n">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O47" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O49" t="n">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O52" t="n">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O53" t="n">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O54" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O55" t="n">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O57" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O58" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -5566,7 +5566,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O60" t="n">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O61" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O62" t="n">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O63" t="n">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O64" t="n">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O65" t="n">
@@ -6076,7 +6076,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O66" t="n">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O67" t="n">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O69" t="n">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O71" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O73" t="n">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O74" t="n">
@@ -6841,7 +6841,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O75" t="n">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O76" t="n">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O77" t="n">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O79" t="n">
@@ -7266,7 +7266,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O80" t="n">
@@ -7351,7 +7351,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O81" t="n">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O82" t="n">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O83" t="n">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O84" t="n">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O85" t="n">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O86" t="n">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O87" t="n">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O88" t="n">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O89" t="n">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O90" t="n">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O91" t="n">
@@ -8286,7 +8286,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O92" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O93" t="n">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O94" t="n">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O95" t="n">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O96" t="n">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O97" t="n">
@@ -8796,7 +8796,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O98" t="n">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O99" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O100" t="n">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O101" t="n">
@@ -9136,7 +9136,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O102" t="n">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O103" t="n">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O104" t="n">
@@ -9391,7 +9391,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O105" t="n">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O106" t="n">
@@ -9561,7 +9561,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O107" t="n">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O108" t="n">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O109" t="n">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O110" t="n">
@@ -9901,7 +9901,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O111" t="n">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O112" t="n">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O113" t="n">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O114" t="n">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O115" t="n">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O116" t="n">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O117" t="n">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O118" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O119" t="n">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O120" t="n">
@@ -10751,7 +10751,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O121" t="n">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O122" t="n">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O123" t="n">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O124" t="n">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O125" t="n">
@@ -11156,7 +11156,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O126" t="n">
@@ -11237,7 +11237,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O128" t="n">
@@ -11399,7 +11399,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O129" t="n">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O130" t="n">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O131" t="n">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O132" t="n">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O133" t="n">
@@ -11804,7 +11804,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O134" t="n">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O135" t="n">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O136" t="n">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O137" t="n">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O138" t="n">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O139" t="n">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O140" t="n">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O141" t="n">
@@ -12452,7 +12452,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O142" t="n">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O143" t="n">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O144" t="n">
@@ -12695,7 +12695,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O145" t="n">
@@ -12776,7 +12776,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O146" t="n">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O147" t="n">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O148" t="n">
@@ -13019,7 +13019,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O149" t="n">
@@ -13100,7 +13100,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O150" t="n">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O151" t="n">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O152" t="n">
@@ -13343,7 +13343,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O153" t="n">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O154" t="n">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O155" t="n">
@@ -13586,7 +13586,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O156" t="n">
@@ -13667,7 +13667,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O157" t="n">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O158" t="n">
@@ -13829,7 +13829,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O159" t="n">
@@ -13910,7 +13910,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O160" t="n">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O161" t="n">
@@ -14072,7 +14072,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O162" t="n">
@@ -14153,7 +14153,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O163" t="n">
@@ -14234,7 +14234,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O164" t="n">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O165" t="n">
@@ -14396,7 +14396,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O166" t="n">
@@ -14477,7 +14477,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O167" t="n">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O168" t="n">
@@ -14639,7 +14639,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O169" t="n">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O170" t="n">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O171" t="n">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O172" t="n">
@@ -14963,7 +14963,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O173" t="n">
@@ -15044,7 +15044,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O174" t="n">
@@ -15125,7 +15125,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O175" t="n">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O176" t="n">
@@ -15287,7 +15287,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O177" t="n">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O178" t="n">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O179" t="n">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O180" t="n">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>d7-local-template-v2.2-validation-graded</t>
+          <t>d7-local-template-v2.3-family-node-validation</t>
         </is>
       </c>
       <c r="O181" t="n">
@@ -29377,20 +29377,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:S57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="29" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="45" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="29" customWidth="1" min="16" max="16"/>
+    <col width="34" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29406,45 +29414,85 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>family_support_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>family_support_level</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>node_support_level</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>node_validation_passed</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>support_level</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>n_effective</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>support_level</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>node_n_effective</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>node_reference_coverage</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>node_bootstrap_stability</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>node_holdout_far</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>profile_covariance_mode</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>alpha_floor</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>alpha_used</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>covariance_condition_number</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>limited_support_exit_status</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>exit_failed_reasons</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>veto_eligible</t>
         </is>
@@ -29461,39 +29509,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>D7-ORP-R0-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>76</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>76</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.8853390169491939</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
         <v>2.34344395669909</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K2" t="b">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29508,39 +29586,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>D7-ORP-R1-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>71</v>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>71</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.8936379940429484</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2112676056338028</v>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
         <v>1.658152502991723</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K3" t="b">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29555,39 +29663,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>D7-ORP-R2-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>29</v>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.8313066687385422</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="N4" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
         <v>10.91503976643994</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K4" t="b">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_blocked_holdouts</t>
+        </is>
+      </c>
+      <c r="S4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29602,39 +29740,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>D7-ORP-R3-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>46</v>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>46</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.8723400061031292</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
         <v>60.08553334435669</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29649,39 +29817,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>D7-ORP-R0-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>76</v>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>76</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.900857222300845</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
         <v>2.34344395669909</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K6" t="b">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29696,39 +29894,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D7-ORP-R1-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>71</v>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>71</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.8906047025829307</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1267605633802817</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
         <v>1.658152502991723</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>holdout_far</t>
         </is>
       </c>
-      <c r="K7" t="b">
+      <c r="S7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29743,39 +29971,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>D7-ORP-R2-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>29</v>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>29</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.8050556135558764</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
         <v>10.91503976643994</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K8" t="b">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29790,39 +30048,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>D7-ORP-R3-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>46</v>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>46</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.8208820294228981</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="N9" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
         <v>60.08553334435669</v>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K9" t="b">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_blocked_holdouts</t>
+        </is>
+      </c>
+      <c r="S9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29837,39 +30125,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>D7-ORP-R0-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>76</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>76</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8944676951329199</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.07894736842105263</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="N10" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" t="n">
         <v>2.34344395669909</v>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>holdout_far</t>
         </is>
       </c>
-      <c r="K10" t="b">
+      <c r="S10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29884,39 +30202,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>D7-ORP-R1-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>71</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>71</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8463329427292223</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.2676056338028169</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" t="n">
         <v>1.658152502991723</v>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K11" t="b">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29931,39 +30279,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>D7-ORP-R2-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>29</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.8058294131267864</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
         <v>10.91503976643994</v>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K12" t="b">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S12" t="b">
         <v>0</v>
       </c>
     </row>
@@ -29978,39 +30356,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D7-ORP-R3-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>46</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>46</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7172149383562785</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" t="n">
         <v>60.08553334435669</v>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K13" t="b">
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30025,39 +30433,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>D7-DO-R0-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>76</v>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>76</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.8410425034849194</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.07894736842105263</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
         <v>4548632244.376826</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>statistical_action_candidate</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>family_and_node_action_candidate</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K14" t="b">
+      <c r="S14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30072,39 +30510,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>D7-DO-R1-full_shrinkage-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>71</v>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>71</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.8936193169093209</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.352112676056338</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>full_shrinkage</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>0.0004298512162779192</v>
       </c>
-      <c r="H15" t="n">
+      <c r="P15" t="n">
         <v>586.3983258039873</v>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K15" t="b">
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30119,39 +30587,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>D7-DO-R2-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
         <v>29</v>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="I16" t="n">
+        <v>29</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.7457152588752606</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" t="n">
         <v>646.3054840670832</v>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
-        </is>
-      </c>
-      <c r="K16" t="b">
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30166,39 +30664,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D7-DO-R3-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>46</v>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>46</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.8577916014822848</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" t="n">
         <v>171822144.318474</v>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K17" t="b">
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30213,39 +30741,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>D7-DO-R0-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
         <v>76</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>76</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.9061820943982193</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.3026315789473684</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="n">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" t="n">
         <v>4548632244.376826</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>statistical_action_candidate</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="K18" t="b">
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>scientific_score_ready</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30260,39 +30818,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D7-DO-R1-full_shrinkage-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
         <v>71</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>71</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.8792308050813656</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.1408450704225352</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>full_shrinkage</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.0004298512162779192</v>
       </c>
-      <c r="H19" t="n">
+      <c r="P19" t="n">
         <v>586.3983258039873</v>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>holdout_far</t>
         </is>
       </c>
-      <c r="K19" t="b">
+      <c r="S19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30307,39 +30895,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>D7-DO-R2-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
         <v>29</v>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>29</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.7911469551281255</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" t="n">
         <v>646.3054840670832</v>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
-        </is>
-      </c>
-      <c r="K20" t="b">
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30354,39 +30972,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>D7-DO-R3-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
         <v>46</v>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="I21" t="n">
+        <v>46</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.738624119226148</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" t="n">
         <v>171822144.318474</v>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K21" t="b">
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts</t>
+        </is>
+      </c>
+      <c r="S21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30401,39 +31049,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>D7-DO-R0-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
         <v>76</v>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="I22" t="n">
+        <v>76</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.8797334465554039</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.1184210526315789</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" t="n">
         <v>4548632244.376826</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>statistical_action_candidate</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>family_and_node_action_candidate</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K22" t="b">
+      <c r="S22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30448,39 +31126,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D7-DO-R1-full_shrinkage-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
         <v>71</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
+      <c r="I23" t="n">
+        <v>71</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.8946601459414483</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2535211267605634</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>full_shrinkage</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>0.0004298512162779192</v>
       </c>
-      <c r="H23" t="n">
+      <c r="P23" t="n">
         <v>586.3983258039873</v>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K23" t="b">
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30495,39 +31203,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>D7-DO-R2-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
         <v>29</v>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
+      <c r="I24" t="n">
+        <v>29</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.770810077427203</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="N24" t="n">
+        <v>1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" t="n">
         <v>646.3054840670832</v>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
-        </is>
-      </c>
-      <c r="K24" t="b">
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30542,39 +31280,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D7-DO-R3-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
         <v>46</v>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="I25" t="n">
+        <v>46</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.8132666335999502</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1</v>
+      </c>
+      <c r="P25" t="n">
         <v>171822144.318474</v>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K25" t="b">
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30589,39 +31357,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>D7-DO-R0-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
         <v>76</v>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="I26" t="n">
+        <v>76</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.5851660866396985</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="M26" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
+      <c r="P26" t="n">
         <v>4548632244.376826</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>statistical_action_candidate</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="K26" t="b">
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>scientific_score_ready</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>node_bootstrap_stability</t>
+        </is>
+      </c>
+      <c r="S26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30636,39 +31434,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>D7-DO-R1-full_shrinkage-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
         <v>71</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="I27" t="n">
+        <v>71</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.7328635397631305</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.2957746478873239</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>full_shrinkage</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
         <v>0.0004298512162779192</v>
       </c>
-      <c r="H27" t="n">
+      <c r="P27" t="n">
         <v>586.3983258039873</v>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K27" t="b">
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>holdout_far|node_bootstrap_stability|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30683,39 +31511,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>D7-DO-R2-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
         <v>29</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
+      <c r="I28" t="n">
+        <v>29</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.4393147781620633</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
         <v>646.3054840670832</v>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
-        </is>
-      </c>
-      <c r="K28" t="b">
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts</t>
+        </is>
+      </c>
+      <c r="S28" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30730,39 +31588,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>D7-DO-R3-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F29" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
         <v>46</v>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
+      <c r="I29" t="n">
+        <v>46</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.4769244226614046</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="M29" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="n">
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1</v>
+      </c>
+      <c r="P29" t="n">
         <v>171822144.318474</v>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K29" t="b">
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts</t>
+        </is>
+      </c>
+      <c r="S29" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30777,39 +31665,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>D7-ORP-R0-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
         <v>76</v>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
+      <c r="I30" t="n">
+        <v>76</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.9080005753374649</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.2763157894736842</v>
+      </c>
+      <c r="M30" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" t="n">
+      <c r="N30" t="n">
+        <v>1</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" t="n">
         <v>2.34344395669909</v>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K30" t="b">
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S30" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30824,39 +31742,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>D7-ORP-R1-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
         <v>71</v>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="I31" t="n">
+        <v>71</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.7870619307896956</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.3802816901408451</v>
+      </c>
+      <c r="M31" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>1</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="n">
+      <c r="N31" t="n">
+        <v>1</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1</v>
+      </c>
+      <c r="P31" t="n">
         <v>1.658152502991723</v>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K31" t="b">
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>holdout_far|node_bootstrap_stability|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S31" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30871,39 +31819,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C32" t="n">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>D7-ORP-R2-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
         <v>29</v>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="I32" t="n">
+        <v>29</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.7745433466667392</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="n">
+      <c r="N32" t="n">
+        <v>1</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
         <v>10.91503976643994</v>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K32" t="b">
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts</t>
+        </is>
+      </c>
+      <c r="S32" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30918,39 +31896,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>D7-ORP-R3-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
         <v>46</v>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="I33" t="n">
+        <v>46</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.8346683155670751</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="M33" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" t="n">
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" t="n">
         <v>60.08553334435669</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K33" t="b">
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S33" t="b">
         <v>0</v>
       </c>
     </row>
@@ -30965,39 +31973,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>D7-ORP-R0-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
         <v>76</v>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="I34" t="n">
+        <v>76</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.869023677122915</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.3421052631578947</v>
+      </c>
+      <c r="M34" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>1</v>
-      </c>
-      <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="n">
+      <c r="N34" t="n">
+        <v>1</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
         <v>2.34344395669909</v>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K34" t="b">
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S34" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31012,39 +32050,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>D7-ORP-R1-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
         <v>71</v>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="I35" t="n">
+        <v>71</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.8667278380698045</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.5211267605633803</v>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="n">
+      <c r="N35" t="n">
+        <v>1</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1</v>
+      </c>
+      <c r="P35" t="n">
         <v>1.658152502991723</v>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K35" t="b">
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S35" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31059,39 +32127,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>D7-ORP-R2-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
         <v>29</v>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="I36" t="n">
+        <v>29</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.7225840694873753</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="n">
+      <c r="N36" t="n">
+        <v>1</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" t="n">
         <v>10.91503976643994</v>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K36" t="b">
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S36" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31106,39 +32204,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>D7-ORP-R3-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
         <v>46</v>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
+      <c r="I37" t="n">
+        <v>46</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.8475379829836671</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="n">
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
         <v>60.08553334435669</v>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K37" t="b">
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S37" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31153,39 +32281,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>D7-ORP-R0-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
         <v>76</v>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="I38" t="n">
+        <v>76</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.845682758617152</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.2105263157894737</v>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="n">
+      <c r="N38" t="n">
+        <v>1</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
         <v>2.34344395669909</v>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K38" t="b">
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S38" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31200,39 +32358,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>D7-ORP-R1-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F39" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
         <v>71</v>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
+      <c r="I39" t="n">
+        <v>71</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.8676047354631962</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.2676056338028169</v>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" t="n">
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" t="n">
         <v>1.658152502991723</v>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K39" t="b">
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S39" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31247,39 +32435,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>D7-ORP-R2-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F40" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
         <v>29</v>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
+      <c r="I40" t="n">
+        <v>29</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.8647869156159191</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" t="n">
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1</v>
+      </c>
+      <c r="P40" t="n">
         <v>10.91503976643994</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K40" t="b">
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|holdout_far|node_effective_blocks|node_distinct_months|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S40" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31294,39 +32512,69 @@
           <t>ORP</t>
         </is>
       </c>
-      <c r="C41" t="n">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>D7-ORP-R3-diagonal_robust_z-variable_public</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
         <v>46</v>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
+      <c r="I41" t="n">
+        <v>46</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.6724026453443794</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="n">
-        <v>1</v>
-      </c>
-      <c r="H41" t="n">
+      <c r="N41" t="n">
+        <v>1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1</v>
+      </c>
+      <c r="P41" t="n">
         <v>60.08553334435669</v>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>effective_blocks|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K41" t="b">
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>effective_blocks|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S41" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31341,39 +32589,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C42" t="n">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>D7-DO-R0-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F42" t="b">
+        <v>0</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
         <v>76</v>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="I42" t="n">
+        <v>76</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.8985977255968349</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.3947368421052632</v>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H42" t="n">
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1</v>
+      </c>
+      <c r="P42" t="n">
         <v>4548632244.376826</v>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>statistical_action_candidate</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="K42" t="b">
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>scientific_score_ready</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S42" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31388,39 +32666,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C43" t="n">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>D7-DO-R1-full_shrinkage-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F43" t="b">
+        <v>0</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
         <v>71</v>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="I43" t="n">
+        <v>71</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.906136239164314</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.4366197183098591</v>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>full_shrinkage</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
         <v>0.0004298512162779192</v>
       </c>
-      <c r="H43" t="n">
+      <c r="P43" t="n">
         <v>586.3983258039873</v>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K43" t="b">
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S43" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31435,39 +32743,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C44" t="n">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>D7-DO-R2-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F44" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
         <v>29</v>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="I44" t="n">
+        <v>29</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.7097137453332778</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44" t="n">
+      <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1</v>
+      </c>
+      <c r="P44" t="n">
         <v>646.3054840670832</v>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
-        </is>
-      </c>
-      <c r="K44" t="b">
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S44" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31482,39 +32820,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C45" t="n">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>D7-DO-R3-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F45" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
         <v>46</v>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
+      <c r="I45" t="n">
+        <v>46</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.8748058494886271</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1</v>
-      </c>
-      <c r="H45" t="n">
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>1</v>
+      </c>
+      <c r="P45" t="n">
         <v>171822144.318474</v>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K45" t="b">
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts</t>
+        </is>
+      </c>
+      <c r="S45" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31529,39 +32897,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C46" t="n">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>D7-DO-R0-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
         <v>76</v>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="I46" t="n">
+        <v>76</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.8517373760269955</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.1052631578947368</v>
+      </c>
+      <c r="M46" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" t="n">
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1</v>
+      </c>
+      <c r="P46" t="n">
         <v>4548632244.376826</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>statistical_action_candidate</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>family_and_node_action_candidate</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="K46" t="b">
+      <c r="S46" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31576,39 +32974,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C47" t="n">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>D7-DO-R1-full_shrinkage-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
         <v>71</v>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="I47" t="n">
+        <v>71</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.8660679758495219</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.1830985915492958</v>
+      </c>
+      <c r="M47" t="inlineStr">
         <is>
           <t>full_shrinkage</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
         <v>0.0004298512162779192</v>
       </c>
-      <c r="H47" t="n">
+      <c r="P47" t="n">
         <v>586.3983258039873</v>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K47" t="b">
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S47" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31623,39 +33051,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C48" t="n">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>D7-DO-R2-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
         <v>29</v>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
+      <c r="I48" t="n">
+        <v>29</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.6674378429723318</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" t="n">
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" t="n">
         <v>646.3054840670832</v>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
-        </is>
-      </c>
-      <c r="K48" t="b">
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S48" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31670,39 +33128,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C49" t="n">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>D7-DO-R3-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
         <v>46</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="I49" t="n">
+        <v>46</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.8829888096982755</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" t="n">
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" t="n">
         <v>171822144.318474</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K49" t="b">
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S49" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31717,39 +33205,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C50" t="n">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>D7-DO-R0-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
         <v>76</v>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
+      <c r="I50" t="n">
+        <v>76</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.8296618710173502</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.1842105263157895</v>
+      </c>
+      <c r="M50" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50" t="n">
+      <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
         <v>4548632244.376826</v>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>statistical_action_candidate</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="K50" t="b">
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>scientific_score_ready</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S50" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31764,39 +33282,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C51" t="n">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>D7-DO-R1-full_shrinkage-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
         <v>71</v>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="I51" t="n">
+        <v>71</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.8905227772632321</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.2816901408450704</v>
+      </c>
+      <c r="M51" t="inlineStr">
         <is>
           <t>full_shrinkage</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
         <v>0.0004298512162779192</v>
       </c>
-      <c r="H51" t="n">
+      <c r="P51" t="n">
         <v>586.3983258039873</v>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K51" t="b">
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S51" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31811,39 +33359,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C52" t="n">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>D7-DO-R2-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
         <v>29</v>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="I52" t="n">
+        <v>29</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.7450583536465611</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="M52" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H52" t="n">
+      <c r="N52" t="n">
+        <v>1</v>
+      </c>
+      <c r="O52" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" t="n">
         <v>646.3054840670832</v>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
-        </is>
-      </c>
-      <c r="K52" t="b">
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S52" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31858,39 +33436,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C53" t="n">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>D7-DO-R3-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
         <v>46</v>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
+      <c r="I53" t="n">
+        <v>46</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.8697786764309048</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" t="n">
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
         <v>171822144.318474</v>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K53" t="b">
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S53" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31905,39 +33513,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C54" t="n">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>D7-DO-R0-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
         <v>76</v>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>L3</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
+      <c r="I54" t="n">
+        <v>76</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.9950738916256158</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.8612234067438752</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="M54" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" t="n">
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
         <v>4548632244.376826</v>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>statistical_action_candidate</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="K54" t="b">
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>scientific_score_ready</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S54" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31952,39 +33590,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>D7-DO-R1-full_shrinkage-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
         <v>71</v>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
+      <c r="I55" t="n">
+        <v>71</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.8586202036181716</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.1690140845070423</v>
+      </c>
+      <c r="M55" t="inlineStr">
         <is>
           <t>full_shrinkage</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
         <v>0.0004298512162779192</v>
       </c>
-      <c r="H55" t="n">
+      <c r="P55" t="n">
         <v>586.3983258039873</v>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>holdout_far</t>
-        </is>
-      </c>
-      <c r="K55" t="b">
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>holdout_far|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S55" t="b">
         <v>0</v>
       </c>
     </row>
@@ -31999,39 +33667,69 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>D7-DO-R2-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
         <v>29</v>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
+      <c r="I56" t="n">
+        <v>29</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.9994662396583934</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.5956346711026141</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" t="n">
-        <v>1</v>
-      </c>
-      <c r="H56" t="n">
+      <c r="N56" t="n">
+        <v>1</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" t="n">
         <v>646.3054840670832</v>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>diagnostic_only</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>effective_blocks|distinct_months|blocked_holdouts</t>
-        </is>
-      </c>
-      <c r="K56" t="b">
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>effective_blocks|distinct_months|blocked_holdouts|node_effective_blocks|node_distinct_months|node_bootstrap_stability|node_blocked_holdouts|node_holdout_far</t>
+        </is>
+      </c>
+      <c r="S56" t="b">
         <v>0</v>
       </c>
     </row>
@@ -32046,44 +33744,74 @@
           <t>DO</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>D7-DO-R3-diagonal_robust_z-variable_regime_zone</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="F57" t="b">
+        <v>0</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
         <v>46</v>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>L2</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
+      <c r="I57" t="n">
+        <v>46</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.9897144883844653</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.7319136629089084</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.1333333333333333</v>
+      </c>
+      <c r="M57" t="inlineStr">
         <is>
           <t>diagonal_robust_z</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57" t="n">
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
         <v>171822144.318474</v>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>scientific_score_ready</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far</t>
-        </is>
-      </c>
-      <c r="K57" t="b">
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>effective_blocks|bootstrap_stability|blocked_holdouts|holdout_far|node_bootstrap_stability|node_blocked_holdouts</t>
+        </is>
+      </c>
+      <c r="S57" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K57"/>
+  <autoFilter ref="A1:S57"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32228,10 +33956,10 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="27" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
@@ -32270,7 +33998,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55.16474209993612</v>
+        <v>57.544138199999</v>
       </c>
       <c r="B2" t="n">
         <v>180</v>
@@ -32279,7 +34007,7 @@
         <v>360</v>
       </c>
       <c r="D2" t="n">
-        <v>9.788860443594441</v>
+        <v>9.384100182289801</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
